--- a/test_data/v2/demo/dimpolicy_universal.xlsx
+++ b/test_data/v2/demo/dimpolicy_universal.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="StockBalances" sheetId="1" state="visible" r:id="rId3"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="259">
   <si>
     <t xml:space="preserve">Item ID</t>
   </si>
@@ -747,6 +747,9 @@
     <t xml:space="preserve">CSVDelimiter</t>
   </si>
   <si>
+    <t xml:space="preserve">CSVEncoding</t>
+  </si>
+  <si>
     <t xml:space="preserve">test_data/v2/demo/items_universal.csv</t>
   </si>
   <si>
@@ -754,6 +757,9 @@
   </si>
   <si>
     <t xml:space="preserve">;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">utf-8</t>
   </si>
   <si>
     <t xml:space="preserve">test_data/v2/demo/whs_units.xlsx</t>
@@ -889,7 +895,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -947,6 +953,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3870,7 +3880,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.3"/>
@@ -3879,7 +3889,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="6.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3901,7 +3912,10 @@
       <c r="F1" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>160</v>
       </c>
     </row>
@@ -3910,19 +3924,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>163</v>
       </c>
       <c r="D2" s="10"/>
       <c r="E2" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3931,19 +3948,20 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>202</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="4" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3952,19 +3970,20 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>220</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="4" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3973,7 +3992,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>223</v>
@@ -3982,10 +4001,11 @@
         <v>223</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3"/>
+      <c r="H5" s="4" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3994,18 +4014,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="G6" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4037,23 +4060,23 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="s">
-        <v>250</v>
+      <c r="A1" s="16" t="s">
+        <v>252</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>160</v>
@@ -4067,11 +4090,11 @@
         <v>206</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D2" s="16"/>
+        <v>257</v>
+      </c>
+      <c r="D2" s="17"/>
       <c r="E2" s="3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3" t="s">
